--- a/xls/square_un_16_tri3_13_0.xlsx
+++ b/xls/square_un_16_tri3_13_0.xlsx
@@ -482,13 +482,13 @@
         <v>1842</v>
       </c>
       <c r="I16">
-        <v>-1.4068059867090226</v>
+        <v>-1.9006903269261357</v>
       </c>
       <c r="J16">
-        <v>-0.7908550084596248</v>
+        <v>-1.640189164114306</v>
       </c>
       <c r="K16">
-        <v>-0.7162976277509502</v>
+        <v>-0.2458855442197655</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_13_0.xlsx
+++ b/xls/square_un_16_tri3_13_0.xlsx
@@ -461,34 +461,34 @@
         <v>11</v>
       </c>
       <c r="B16">
-        <v>238</v>
+        <v>209</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
       </c>
       <c r="D16">
-        <v>340</v>
+        <v>297</v>
       </c>
       <c r="E16" t="s">
         <v>12</v>
       </c>
       <c r="F16">
-        <v>340</v>
+        <v>297</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
       </c>
       <c r="H16">
-        <v>1842</v>
+        <v>1596</v>
       </c>
       <c r="I16">
-        <v>-1.9006903269261357</v>
+        <v>-1.9452940047841667</v>
       </c>
       <c r="J16">
-        <v>-1.640189164114306</v>
+        <v>-1.6552733770238894</v>
       </c>
       <c r="K16">
-        <v>-0.2458855442197655</v>
+        <v>-0.33163079274956864</v>
       </c>
     </row>
   </sheetData>
